--- a/questionnaire_templates/031_owner_trauma_assessment_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/031_owner_trauma_assessment_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -687,7 +687,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mental_health_counseling</t>
+          <t>mental health counseling</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>case_maintenance</t>
+          <t>case maintenance</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>case_management</t>
+          <t>case management</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>crisis_intervention</t>
+          <t>crisis intervention</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>education_and_training</t>
+          <t>education and training</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>financial_assistance</t>
+          <t>financial assistance</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>housing_assistance</t>
+          <t>housing assistance</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical_services</t>
+          <t>medical services</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>peer_support</t>
+          <t>peer support</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>practical_assistance</t>
+          <t>practical assistance</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>case_maintenance</t>
+          <t>case maintenance</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>case_management</t>
+          <t>case management</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>crisis_intervention</t>
+          <t>crisis intervention</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>education_and_training</t>
+          <t>education and training</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>financial_assistance</t>
+          <t>financial assistance</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>housing_assistance</t>
+          <t>housing assistance</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>medical_services</t>
+          <t>medical services</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>peer_support</t>
+          <t>peer support</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>practical_assistance</t>
+          <t>practical assistance</t>
         </is>
       </c>
     </row>
